--- a/N1C_projects.xlsx
+++ b/N1C_projects.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_708CA2C4BB570B5A851A20FED16579AAF8F451E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD89490B-97A3-40B9-8C51-2414F2D44E22}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_708CA2C4BB570B5A851A20FED16579AAF8F451E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C35E4B8F-BFD5-478A-83B9-BE0009680C30}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
     <sheet name="Variant Assessments" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gene Registry'!$A$1:$AJ$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gene Registry'!$A$1:$AJ$61</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,6 @@
   <authors>
     <author>tc={4bb3d295-2eef-4544-ab5c-7f4f16326ccc}</author>
     <author>tc={a236cffa-7e2c-4ca1-903d-7790f27234e0}</author>
-    <author>tc={374e77fe-8e3d-428f-a5a0-ff55c64da29b}</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0" shapeId="0" xr:uid="{4BB3D295-2EEF-4544-AB5C-7F4F16326CCC}">
@@ -61,20 +60,12 @@
     edited; leaving this here for future reference or to restore some nomenclature if desired:  r.420_421ins[420+795_420+918], p.Lys140_Ala141ins*22</t>
       </text>
     </comment>
-    <comment ref="D38" authorId="2" shapeId="0" xr:uid="{374E77FE-8E3D-428F-A5A0-FF55C64DA29B}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    I think this ASO later failed in clinical trials, so we somehow need to note that down.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="843">
   <si>
     <t>ID</t>
   </si>
@@ -991,7 +982,127 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/22656320/</t>
   </si>
   <si>
-    <t>AP4M1 (SPG50)</t>
+    <t>CPS1</t>
+  </si>
+  <si>
+    <t>NM_001875.5</t>
+  </si>
+  <si>
+    <t>c.1003C&gt;T</t>
+  </si>
+  <si>
+    <t>p.Gln335*</t>
+  </si>
+  <si>
+    <t>Rebecca Ahrens-Nicklas</t>
+  </si>
+  <si>
+    <t>Children’s Hospital of Philadelphia</t>
+  </si>
+  <si>
+    <t>ahrensnicklasr@chop.edu</t>
+  </si>
+  <si>
+    <t>Gene editing</t>
+  </si>
+  <si>
+    <t>Liver</t>
+  </si>
+  <si>
+    <t>https://www.nejm.org/doi/full/10.1056/NEJMoa2504747</t>
+  </si>
+  <si>
+    <t>10.28.2025</t>
+  </si>
+  <si>
+    <t>EHMT2</t>
+  </si>
+  <si>
+    <t>NM_006709.5</t>
+  </si>
+  <si>
+    <t>c.3229G&gt;T</t>
+  </si>
+  <si>
+    <t>p.Ala1077Ser</t>
+  </si>
+  <si>
+    <t>Preprint</t>
+  </si>
+  <si>
+    <t>Maria J. Barrero</t>
+  </si>
+  <si>
+    <t>Spanish National Institute of Health Carlos III (ISCIII)</t>
+  </si>
+  <si>
+    <t>mj.barrero@isciii.es</t>
+  </si>
+  <si>
+    <t>https://www.biorxiv.org/content/10.1101/2025.09.25.678439v1</t>
+  </si>
+  <si>
+    <t>11.7.2025</t>
+  </si>
+  <si>
+    <t>GNAO1</t>
+  </si>
+  <si>
+    <t>NM_020988.3</t>
+  </si>
+  <si>
+    <t>c.736_738delinsAAA</t>
+  </si>
+  <si>
+    <t>p.Glu246Lys</t>
+  </si>
+  <si>
+    <t>Nofar Mor</t>
+  </si>
+  <si>
+    <t>Sheba Medical Center</t>
+  </si>
+  <si>
+    <t>nofar.mor@sheba.health.gov.il</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39897576/</t>
+  </si>
+  <si>
+    <t>Yes, both</t>
+  </si>
+  <si>
+    <t>1.23.2026</t>
+  </si>
+  <si>
+    <t>PACS2</t>
+  </si>
+  <si>
+    <t>NM_001100913.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c.625G&gt;A </t>
+  </si>
+  <si>
+    <t>p.Glu209Lys</t>
+  </si>
+  <si>
+    <t>Heather Olson</t>
+  </si>
+  <si>
+    <t>Department of Neurology, Boston Children's Hospital</t>
+  </si>
+  <si>
+    <t>heather.olson@childrens.harvard.edu</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/29656858/</t>
+  </si>
+  <si>
+    <t>2.24.2026</t>
+  </si>
+  <si>
+    <t>AP4M1</t>
   </si>
   <si>
     <t>NM_004722.4</t>
@@ -1000,9 +1111,6 @@
     <t>SickKids</t>
   </si>
   <si>
-    <t>SickKids Toronto</t>
-  </si>
-  <si>
     <t>Gene replacement</t>
   </si>
   <si>
@@ -1010,129 +1118,6 @@
   </si>
   <si>
     <t>https://pubmed.ncbi.nlm.nih.gov/38942994/</t>
-  </si>
-  <si>
-    <t>CPS1</t>
-  </si>
-  <si>
-    <t>NM_001875.5</t>
-  </si>
-  <si>
-    <t>c.1003C&gt;T</t>
-  </si>
-  <si>
-    <t>p.Gln335*</t>
-  </si>
-  <si>
-    <t>Rebecca Ahrens-Nicklas</t>
-  </si>
-  <si>
-    <t>Children’s Hospital of Philadelphia</t>
-  </si>
-  <si>
-    <t>ahrensnicklasr@chop.edu</t>
-  </si>
-  <si>
-    <t>Gene editing</t>
-  </si>
-  <si>
-    <t>Liver</t>
-  </si>
-  <si>
-    <t>https://www.nejm.org/doi/full/10.1056/NEJMoa2504747</t>
-  </si>
-  <si>
-    <t>10.28.2025</t>
-  </si>
-  <si>
-    <t>EHMT2</t>
-  </si>
-  <si>
-    <t>NM_006709.5</t>
-  </si>
-  <si>
-    <t>c.3229G&gt;T</t>
-  </si>
-  <si>
-    <t>p.Ala1077Ser</t>
-  </si>
-  <si>
-    <t>Preprint</t>
-  </si>
-  <si>
-    <t>Maria J. Barrero</t>
-  </si>
-  <si>
-    <t>Spanish National Institute of Health Carlos III (ISCIII)</t>
-  </si>
-  <si>
-    <t>mj.barrero@isciii.es</t>
-  </si>
-  <si>
-    <t>https://www.biorxiv.org/content/10.1101/2025.09.25.678439v1</t>
-  </si>
-  <si>
-    <t>11.7.2025</t>
-  </si>
-  <si>
-    <t>GNAO1</t>
-  </si>
-  <si>
-    <t>NM_020988.3</t>
-  </si>
-  <si>
-    <t>c.736_738delinsAAA</t>
-  </si>
-  <si>
-    <t>p.Glu246Lys</t>
-  </si>
-  <si>
-    <t>Nofar Mor</t>
-  </si>
-  <si>
-    <t>Sheba Medical Center</t>
-  </si>
-  <si>
-    <t>nofar.mor@sheba.health.gov.il</t>
-  </si>
-  <si>
-    <t>https://pubmed.ncbi.nlm.nih.gov/39897576/</t>
-  </si>
-  <si>
-    <t>Yes, both</t>
-  </si>
-  <si>
-    <t>1.23.2026</t>
-  </si>
-  <si>
-    <t>PACS2</t>
-  </si>
-  <si>
-    <t>NM_001100913.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c.625G&gt;A </t>
-  </si>
-  <si>
-    <t>p.Glu209Lys</t>
-  </si>
-  <si>
-    <t>Heather Olson</t>
-  </si>
-  <si>
-    <t>Department of Neurology, Boston Children's Hospital</t>
-  </si>
-  <si>
-    <t>heather.olson@childrens.harvard.edu</t>
-  </si>
-  <si>
-    <t>https://pubmed.ncbi.nlm.nih.gov/29656858/</t>
-  </si>
-  <si>
-    <t>2.24.2026</t>
-  </si>
-  <si>
-    <t>AP4M1</t>
   </si>
   <si>
     <t>SPG50</t>
@@ -2859,7 +2844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2941,7 +2926,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3183,9 +3167,6 @@
   <threadedComment ref="H23" dT="2025-07-08T17:08:15.00" personId="{62638C06-5D65-4B27-B7DB-0CDBEA0CAAB4}" id="{90E06B67-6B26-4950-96D5-237F4E5AA1AA}" parentId="{A236CFFA-7E2C-4CA1-903D-7790F27234E0}">
     <text>edited; leaving this here for future reference or to restore some nomenclature if desired:  r.420_421ins[420+795_420+918], p.Lys140_Ala141ins*22</text>
   </threadedComment>
-  <threadedComment ref="D38" dT="2025-05-25T09:05:17.00" personId="{71E1F5FA-903B-47BF-826B-D9D248A93BDC}" id="{374E77FE-8E3D-428F-A5A0-FF55C64DA29B}">
-    <text>I think this ASO later failed in clinical trials, so we somehow need to note that down.</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -3194,7 +3175,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AJ977"/>
+  <dimension ref="A1:AJ965"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -3330,7 +3311,7 @@
       <c r="J2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L2" s="7" t="s">
@@ -3372,7 +3353,7 @@
       <c r="C3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="48" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="9" t="s">
@@ -3393,7 +3374,7 @@
       <c r="J3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L3" s="7" t="s">
@@ -3455,7 +3436,7 @@
       <c r="J4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L4" s="7" t="s">
@@ -3496,7 +3477,7 @@
       <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="48" t="s">
         <v>52</v>
       </c>
       <c r="E5" s="9" t="s">
@@ -3515,7 +3496,7 @@
       <c r="J5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="47" t="s">
+      <c r="K5" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="7" t="s">
@@ -3556,7 +3537,7 @@
       <c r="C6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="48" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="9" t="s">
@@ -3577,7 +3558,7 @@
       <c r="J6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L6" s="7" t="s">
@@ -3618,7 +3599,7 @@
       <c r="C7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="48" t="s">
         <v>61</v>
       </c>
       <c r="E7" s="9" t="s">
@@ -3637,7 +3618,7 @@
       <c r="J7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="47" t="s">
+      <c r="K7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L7" s="7" t="s">
@@ -3678,7 +3659,7 @@
       <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="48" t="s">
         <v>66</v>
       </c>
       <c r="E8" s="9" t="s">
@@ -3697,7 +3678,7 @@
       <c r="J8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="47" t="s">
+      <c r="K8" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L8" s="7" t="s">
@@ -3757,7 +3738,7 @@
       <c r="J9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="47" t="s">
+      <c r="K9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L9" s="7" t="s">
@@ -3822,7 +3803,7 @@
       <c r="J10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="7" t="s">
@@ -3884,7 +3865,7 @@
       <c r="J11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L11" s="7" t="s">
@@ -3946,7 +3927,7 @@
       <c r="J12" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K12" s="47" t="s">
+      <c r="K12" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L12" s="7" t="s">
@@ -4008,7 +3989,7 @@
       <c r="J13" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L13" s="7" t="s">
@@ -4070,7 +4051,7 @@
       <c r="J14" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K14" s="47" t="s">
+      <c r="K14" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L14" s="7" t="s">
@@ -4132,7 +4113,7 @@
       <c r="J15" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K15" s="47" t="s">
+      <c r="K15" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L15" s="7" t="s">
@@ -4192,7 +4173,7 @@
       <c r="J16" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K16" s="47" t="s">
+      <c r="K16" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L16" s="7" t="s">
@@ -4257,7 +4238,7 @@
       <c r="J17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="K17" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L17" s="7" t="s">
@@ -4301,7 +4282,7 @@
       <c r="D18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="47" t="s">
+      <c r="E18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="7" t="s">
@@ -4319,7 +4300,7 @@
       <c r="J18" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K18" s="47" t="s">
+      <c r="K18" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L18" s="7" t="s">
@@ -6034,7 +6015,7 @@
       <c r="D45" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="50" t="s">
+      <c r="E45" s="49" t="s">
         <v>120</v>
       </c>
       <c r="F45" s="13" t="s">
@@ -6425,7 +6406,7 @@
       <c r="J51" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="K51" s="47" t="s">
+      <c r="K51" s="6" t="s">
         <v>271</v>
       </c>
       <c r="L51" s="7" t="s">
@@ -6656,13 +6637,13 @@
       <c r="I55" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J55" s="47" t="s">
+      <c r="J55" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="K55" s="47" t="s">
+      <c r="K55" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="L55" s="47" t="s">
+      <c r="L55" s="6" t="s">
         <v>296</v>
       </c>
       <c r="M55" s="7" t="s">
@@ -6687,9 +6668,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:22" hidden="1">
+    <row r="56" spans="1:22">
       <c r="A56" s="6">
-        <f>A55+1</f>
         <v>79</v>
       </c>
       <c r="B56" s="7" t="s">
@@ -6704,139 +6684,142 @@
       <c r="E56" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
+      <c r="F56" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>301</v>
+      </c>
       <c r="H56" s="7"/>
       <c r="I56" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N56" s="7" t="s">
         <v>33</v>
       </c>
       <c r="O56" s="7"/>
       <c r="P56" s="7" t="s">
-        <v>35</v>
+        <v>306</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R56" s="10" t="s">
-        <v>303</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="R56" s="7"/>
       <c r="S56" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
     </row>
-    <row r="57" spans="1:22" hidden="1">
+    <row r="57" spans="1:22" ht="12.75">
       <c r="A57" s="6">
-        <f>A56+1</f>
         <v>80</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H57" s="7"/>
       <c r="I57" s="7" t="s">
-        <v>23</v>
+        <v>313</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>310</v>
+        <v>314</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>315</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>312</v>
+        <v>32</v>
       </c>
       <c r="N57" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O57" s="7"/>
+        <v>42</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="P57" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q57" s="7" t="s">
-        <v>204</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="Q57" s="7"/>
       <c r="R57" s="7"/>
-      <c r="S57" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="T57" s="7"/>
-      <c r="U57" s="7"/>
+      <c r="S57" s="7"/>
+      <c r="T57" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="58" spans="1:22" ht="12.75">
       <c r="A58" s="6">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7" t="s">
-        <v>320</v>
+        <v>23</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="K58" s="47" t="s">
-        <v>322</v>
+        <v>323</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>324</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M58" s="7" t="s">
         <v>32</v>
       </c>
       <c r="N58" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="O58" s="7" t="s">
         <v>56</v>
@@ -6846,54 +6829,55 @@
       </c>
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
-      <c r="S58" s="7"/>
+      <c r="S58" s="10" t="s">
+        <v>326</v>
+      </c>
       <c r="T58" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="U58" s="7" t="s">
-        <v>38</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="12.75">
       <c r="A59" s="6">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="H59" s="7"/>
+        <v>332</v>
+      </c>
       <c r="I59" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="K59" s="47" t="s">
-        <v>331</v>
+        <v>333</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M59" s="7" t="s">
         <v>32</v>
       </c>
       <c r="N59" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O59" s="7" t="s">
         <v>56</v>
@@ -6902,79 +6886,68 @@
         <v>35</v>
       </c>
       <c r="Q59" s="7"/>
-      <c r="R59" s="7"/>
-      <c r="S59" s="10" t="s">
-        <v>333</v>
-      </c>
+      <c r="R59" s="12"/>
+      <c r="S59" s="12"/>
       <c r="T59" s="10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="U59" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" ht="12.75">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="15">
       <c r="A60" s="6">
         <v>83</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G60" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="I60" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="K60" s="6" t="s">
+      <c r="L60" s="12"/>
+      <c r="M60" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="L60" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="M60" s="7" t="s">
-        <v>32</v>
-      </c>
       <c r="N60" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="O60" s="7" t="s">
-        <v>56</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="O60" s="7"/>
       <c r="P60" s="7" t="s">
         <v>35</v>
       </c>
       <c r="Q60" s="7"/>
-      <c r="R60" s="12"/>
-      <c r="S60" s="12"/>
-      <c r="T60" s="10" t="s">
+      <c r="R60" s="47" t="s">
+        <v>342</v>
+      </c>
+      <c r="S60" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="U60" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" ht="15">
+      <c r="T60" s="12"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22">
       <c r="A61" s="6">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>344</v>
+        <v>265</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>23</v>
@@ -6983,220 +6956,121 @@
         <v>345</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="7"/>
+        <v>346</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="J61" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="L61" s="12"/>
+        <v>350</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>352</v>
+      </c>
       <c r="M61" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N61" s="7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O61" s="7"/>
-      <c r="P61" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
-      <c r="R61" s="48" t="s">
-        <v>303</v>
-      </c>
-      <c r="S61" s="48" t="s">
-        <v>304</v>
-      </c>
-      <c r="T61" s="12"/>
-      <c r="U61" s="7"/>
+      <c r="R61" s="7"/>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="V61" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" hidden="1">
-      <c r="A62" s="6">
-        <v>73</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="I62" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="K62" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="L62" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="M62" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="N62" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="7"/>
-      <c r="T62" s="7"/>
-      <c r="U62" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="V62" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" hidden="1">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
+    </row>
+    <row r="62" spans="1:22">
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+    </row>
+    <row r="63" spans="1:22">
       <c r="S63" s="6"/>
       <c r="T63" s="6"/>
-      <c r="U63" s="6"/>
-    </row>
-    <row r="64" spans="1:22" hidden="1">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="6"/>
-      <c r="Q64" s="6"/>
+    </row>
+    <row r="64" spans="1:22">
       <c r="S64" s="6"/>
       <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
-    </row>
-    <row r="65" spans="1:21" hidden="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="6"/>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
+    </row>
+    <row r="65" spans="19:20">
       <c r="S65" s="6"/>
       <c r="T65" s="6"/>
-      <c r="U65" s="6"/>
-    </row>
-    <row r="66" spans="1:21" hidden="1">
-      <c r="C66" s="8"/>
+    </row>
+    <row r="66" spans="19:20">
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
     </row>
-    <row r="67" spans="1:21" hidden="1">
-      <c r="C67" s="8"/>
+    <row r="67" spans="19:20">
       <c r="S67" s="6"/>
       <c r="T67" s="6"/>
     </row>
-    <row r="68" spans="1:21" hidden="1">
-      <c r="C68" s="8"/>
+    <row r="68" spans="19:20">
       <c r="S68" s="6"/>
       <c r="T68" s="6"/>
     </row>
-    <row r="69" spans="1:21" hidden="1">
-      <c r="C69" s="8"/>
+    <row r="69" spans="19:20">
       <c r="S69" s="6"/>
       <c r="T69" s="6"/>
     </row>
-    <row r="70" spans="1:21" hidden="1">
-      <c r="C70" s="8"/>
+    <row r="70" spans="19:20">
       <c r="S70" s="6"/>
       <c r="T70" s="6"/>
     </row>
-    <row r="71" spans="1:21">
+    <row r="71" spans="19:20">
       <c r="S71" s="6"/>
       <c r="T71" s="6"/>
     </row>
-    <row r="72" spans="1:21">
+    <row r="72" spans="19:20">
       <c r="S72" s="6"/>
       <c r="T72" s="6"/>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="19:20">
       <c r="S73" s="6"/>
       <c r="T73" s="6"/>
     </row>
-    <row r="74" spans="1:21">
+    <row r="74" spans="19:20">
       <c r="S74" s="6"/>
       <c r="T74" s="6"/>
     </row>
-    <row r="75" spans="1:21">
+    <row r="75" spans="19:20">
       <c r="S75" s="6"/>
       <c r="T75" s="6"/>
     </row>
-    <row r="76" spans="1:21">
+    <row r="76" spans="19:20">
       <c r="S76" s="6"/>
       <c r="T76" s="6"/>
     </row>
-    <row r="77" spans="1:21">
+    <row r="77" spans="19:20">
       <c r="S77" s="6"/>
       <c r="T77" s="6"/>
     </row>
-    <row r="78" spans="1:21">
+    <row r="78" spans="19:20">
       <c r="S78" s="6"/>
       <c r="T78" s="6"/>
     </row>
-    <row r="79" spans="1:21">
+    <row r="79" spans="19:20">
       <c r="S79" s="6"/>
       <c r="T79" s="6"/>
     </row>
-    <row r="80" spans="1:21">
+    <row r="80" spans="19:20">
       <c r="S80" s="6"/>
       <c r="T80" s="6"/>
     </row>
@@ -10740,89 +10614,41 @@
       <c r="S965" s="6"/>
       <c r="T965" s="6"/>
     </row>
-    <row r="966" spans="19:20">
-      <c r="S966" s="6"/>
-      <c r="T966" s="6"/>
-    </row>
-    <row r="967" spans="19:20">
-      <c r="S967" s="6"/>
-      <c r="T967" s="6"/>
-    </row>
-    <row r="968" spans="19:20">
-      <c r="S968" s="6"/>
-      <c r="T968" s="6"/>
-    </row>
-    <row r="969" spans="19:20">
-      <c r="S969" s="6"/>
-      <c r="T969" s="6"/>
-    </row>
-    <row r="970" spans="19:20">
-      <c r="S970" s="6"/>
-      <c r="T970" s="6"/>
-    </row>
-    <row r="971" spans="19:20">
-      <c r="S971" s="6"/>
-      <c r="T971" s="6"/>
-    </row>
-    <row r="972" spans="19:20">
-      <c r="S972" s="6"/>
-      <c r="T972" s="6"/>
-    </row>
-    <row r="973" spans="19:20">
-      <c r="S973" s="6"/>
-      <c r="T973" s="6"/>
-    </row>
-    <row r="974" spans="19:20">
-      <c r="S974" s="6"/>
-      <c r="T974" s="6"/>
-    </row>
-    <row r="975" spans="19:20">
-      <c r="S975" s="6"/>
-      <c r="T975" s="6"/>
-    </row>
-    <row r="976" spans="19:20">
-      <c r="S976" s="6"/>
-      <c r="T976" s="6"/>
-    </row>
-    <row r="977" spans="19:20">
-      <c r="S977" s="6"/>
-      <c r="T977" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ70" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:AJ61" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="12">
       <filters>
         <filter val="Antisense oligonucleotide"/>
         <filter val="Other"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AJ70">
-      <sortCondition ref="C1:C70"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AJ61">
+      <sortCondition ref="C1:C61"/>
     </sortState>
   </autoFilter>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q63:Q65 I2:I65 Q2:Q61" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q60 I2:I61" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Yes,No,Unknown,Preprint"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="O8" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Splice Modulating,Knockdown,Tango,Exon Skipping,Cryptic Splicing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O9:O55 O58:O61 O63:O65 O2:O7" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O9:O55 O57:O60 O2:O7" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"Knockdown,Knockdown (allele-selective),Splice correction,Exon Skipping,Exon inclusion,Upregulation from WT allele,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="U55 U58:U65 U2:U51" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="U55 U57:U61 U2:U51" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"Yes, cell line,Yes, mouse model,Yes, both,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C70" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C61" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P65" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P61" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Brain/Spinal cord,Eye,Muscular,Other,Liver,Skin"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N65" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N61" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Under Development,In Consideration for Development,Currently Not Pursued for Development,Developed,Clinical Application,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M65" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M61" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"Antisense oligonucleotide,Gene replacement,Gene editing,RNA editing,Other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10878,35 +10704,33 @@
     <hyperlink ref="S40" r:id="rId49" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
     <hyperlink ref="L41" r:id="rId50" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
     <hyperlink ref="R41" r:id="rId51" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="R56" r:id="rId52" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="S56" r:id="rId53" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="S57" r:id="rId54" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="T42" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="T43" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="T44" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="T45" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="S46" r:id="rId59" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="T46" r:id="rId60" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="S47" r:id="rId61" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="T47" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="S48" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="T48" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="S49" r:id="rId65" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="T49" r:id="rId66" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="T50" r:id="rId67" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="T52" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="T53" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="T54" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="T55" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="T58" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="S59" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="T59" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="T60" r:id="rId75" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="R61" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="S61" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="S56" r:id="rId52" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="T42" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="T43" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="T44" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="T45" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="S46" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="T46" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="S47" r:id="rId59" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="T47" r:id="rId60" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="S48" r:id="rId61" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="T48" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="S49" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="T49" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="T50" r:id="rId65" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="T52" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="T53" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="T54" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="T55" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="T57" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="S58" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="T58" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="T59" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="R60" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="S60" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <legacyDrawing r:id="rId78"/>
+  <legacyDrawing r:id="rId76"/>
 </worksheet>
 </file>
 
@@ -10935,40 +10759,40 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="31" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1" s="32" t="s">
         <v>357</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="F1" s="32" t="s">
         <v>358</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="G1" s="33" t="s">
         <v>359</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="H1" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="I1" s="34" t="s">
         <v>361</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="J1" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="K1" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="L1" s="34" t="s">
         <v>364</v>
-      </c>
-      <c r="K1" s="34" t="s">
-        <v>365</v>
-      </c>
-      <c r="L1" s="34" t="s">
-        <v>366</v>
       </c>
       <c r="M1" s="35" t="s">
         <v>21</v>
@@ -10979,35 +10803,35 @@
         <v>341</v>
       </c>
       <c r="B2" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="D2" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="E2" s="37" t="s">
         <v>368</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="F2" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="G2" s="38" t="s">
         <v>370</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="H2" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="I2" s="37" t="s">
         <v>372</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>374</v>
       </c>
       <c r="J2" s="40"/>
       <c r="K2" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M2" s="35"/>
     </row>
@@ -11016,35 +10840,35 @@
         <v>341</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D3" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>371</v>
+      </c>
+      <c r="I3" s="37" t="s">
         <v>377</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="F3" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="I3" s="37" t="s">
-        <v>379</v>
       </c>
       <c r="J3" s="39"/>
       <c r="K3" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M3" s="35"/>
     </row>
@@ -11053,35 +10877,35 @@
         <v>2928</v>
       </c>
       <c r="B4" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>381</v>
+      </c>
+      <c r="D4" s="37" t="s">
         <v>382</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="E4" s="37" t="s">
         <v>383</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="F4" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>384</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="H4" s="39" t="s">
         <v>385</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G4" s="38" t="s">
+      <c r="I4" s="37" t="s">
         <v>386</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>388</v>
       </c>
       <c r="J4" s="39"/>
       <c r="K4" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M4" s="35"/>
     </row>
@@ -11090,35 +10914,35 @@
         <v>2928</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G5" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="I5" s="37" t="s">
         <v>386</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>388</v>
       </c>
       <c r="J5" s="39"/>
       <c r="K5" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M5" s="35"/>
     </row>
@@ -11127,35 +10951,35 @@
         <v>2928</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D6" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="I6" s="37" t="s">
         <v>393</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="I6" s="37" t="s">
-        <v>395</v>
       </c>
       <c r="J6" s="39"/>
       <c r="K6" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M6" s="35"/>
     </row>
@@ -11164,35 +10988,35 @@
         <v>2928</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G7" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="I7" s="37" t="s">
         <v>386</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>388</v>
       </c>
       <c r="J7" s="39"/>
       <c r="K7" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M7" s="35"/>
     </row>
@@ -11201,35 +11025,35 @@
         <v>11117</v>
       </c>
       <c r="B8" s="37" t="s">
+        <v>398</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>400</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="E8" s="37" t="s">
         <v>401</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="F8" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="38" t="s">
         <v>402</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="H8" s="39" t="s">
         <v>403</v>
       </c>
-      <c r="F8" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G8" s="38" t="s">
+      <c r="I8" s="37" t="s">
         <v>404</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>405</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>406</v>
       </c>
       <c r="J8" s="39"/>
       <c r="K8" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M8" s="35"/>
     </row>
@@ -11238,33 +11062,33 @@
         <v>11179</v>
       </c>
       <c r="B9" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>407</v>
+      </c>
+      <c r="D9" s="37" t="s">
         <v>408</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="E9" s="37" t="s">
         <v>409</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>410</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>411</v>
-      </c>
       <c r="F9" s="37" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H9" s="39"/>
       <c r="I9" s="37" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J9" s="39"/>
       <c r="K9" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L9" s="37" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M9" s="35"/>
     </row>
@@ -11273,37 +11097,37 @@
         <v>12405</v>
       </c>
       <c r="B10" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>414</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>415</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="F10" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H10" s="39" t="s">
         <v>416</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="I10" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="J10" s="39" t="s">
         <v>417</v>
       </c>
-      <c r="F10" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="H10" s="39" t="s">
+      <c r="K10" s="37" t="s">
         <v>418</v>
       </c>
-      <c r="I10" s="37" t="s">
-        <v>406</v>
-      </c>
-      <c r="J10" s="39" t="s">
+      <c r="L10" s="37" t="s">
         <v>419</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>420</v>
-      </c>
-      <c r="L10" s="37" t="s">
-        <v>421</v>
       </c>
       <c r="M10" s="35"/>
     </row>
@@ -11312,35 +11136,35 @@
         <v>12405</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D11" s="37" t="s">
+        <v>420</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>421</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H11" s="39" t="s">
         <v>422</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="I11" s="37" t="s">
         <v>423</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>424</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>425</v>
       </c>
       <c r="J11" s="39"/>
       <c r="K11" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L11" s="37" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M11" s="35"/>
     </row>
@@ -11349,35 +11173,35 @@
         <v>12405</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F12" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H12" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="I12" s="37" t="s">
         <v>372</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>374</v>
       </c>
       <c r="J12" s="39"/>
       <c r="K12" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L12" s="37" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M12" s="35"/>
     </row>
@@ -11386,147 +11210,147 @@
         <v>12405</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F13" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H13" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="G13" s="38" t="s">
+      <c r="I13" s="37" t="s">
         <v>372</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>374</v>
       </c>
       <c r="J13" s="39"/>
       <c r="K13" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L13" s="37" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M13" s="35"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="35"/>
       <c r="B14" s="37" t="s">
+        <v>431</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>432</v>
+      </c>
+      <c r="D14" s="37" t="s">
         <v>433</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="E14" s="37" t="s">
         <v>434</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="F14" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="I14" s="37" t="s">
         <v>435</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="J14" s="39" t="s">
         <v>436</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="I14" s="37" t="s">
+      <c r="K14" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="L14" s="37" t="s">
         <v>437</v>
-      </c>
-      <c r="J14" s="39" t="s">
-        <v>438</v>
-      </c>
-      <c r="K14" s="37" t="s">
-        <v>380</v>
-      </c>
-      <c r="L14" s="37" t="s">
-        <v>439</v>
       </c>
       <c r="M14" s="35"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="35"/>
       <c r="B15" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="D15" s="37" t="s">
         <v>440</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="E15" s="37" t="s">
         <v>441</v>
       </c>
-      <c r="D15" s="37" t="s">
-        <v>442</v>
-      </c>
-      <c r="E15" s="37" t="s">
-        <v>443</v>
-      </c>
       <c r="F15" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H15" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="G15" s="38" t="s">
+      <c r="I15" s="37" t="s">
         <v>372</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>374</v>
       </c>
       <c r="J15" s="39"/>
       <c r="K15" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M15" s="35" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="35"/>
       <c r="B16" s="37" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C16" s="37" t="s">
+        <v>444</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>445</v>
+      </c>
+      <c r="E16" s="37" t="s">
         <v>446</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="F16" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>371</v>
+      </c>
+      <c r="I16" s="37" t="s">
         <v>447</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>448</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="H16" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>449</v>
       </c>
       <c r="J16" s="39"/>
       <c r="K16" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L16" s="37" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -11534,35 +11358,35 @@
         <v>6677</v>
       </c>
       <c r="B17" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="D17" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="E17" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="F17" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="I17" s="37" t="s">
         <v>454</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>455</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>456</v>
       </c>
       <c r="J17" s="39"/>
       <c r="K17" s="37" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L17" s="37" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="M17" s="35"/>
     </row>
@@ -11570,35 +11394,35 @@
       <c r="A18" s="35"/>
       <c r="B18" s="37"/>
       <c r="C18" s="37" t="s">
+        <v>457</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="E18" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="F18" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G18" s="38" t="s">
         <v>460</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="H18" s="39" t="s">
         <v>461</v>
       </c>
-      <c r="F18" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G18" s="38" t="s">
+      <c r="I18" s="37" t="s">
         <v>462</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>463</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>464</v>
       </c>
       <c r="J18" s="39"/>
       <c r="K18" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L18" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -11606,70 +11430,70 @@
         <v>6677</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C19" s="37" t="s">
+        <v>465</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="E19" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="F19" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H19" s="39" t="s">
         <v>468</v>
       </c>
-      <c r="E19" s="37" t="s">
-        <v>469</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>470</v>
-      </c>
       <c r="I19" s="37" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J19" s="39"/>
       <c r="K19" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L19" s="37" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M19" s="35"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="35"/>
       <c r="B20" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>471</v>
+      </c>
+      <c r="D20" s="37" t="s">
         <v>472</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="E20" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="F20" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="H20" s="39" t="s">
         <v>474</v>
       </c>
-      <c r="E20" s="37" t="s">
-        <v>475</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G20" s="38" t="s">
+      <c r="I20" s="37" t="s">
         <v>372</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>476</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>374</v>
       </c>
       <c r="J20" s="39"/>
       <c r="K20" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L20" s="37" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M20" s="35"/>
     </row>
@@ -11677,140 +11501,140 @@
       <c r="A21" s="35"/>
       <c r="B21" s="37"/>
       <c r="C21" s="37" t="s">
+        <v>476</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="E21" s="37" t="s">
         <v>478</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="F21" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="H21" s="39" t="s">
         <v>479</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="I21" s="37" t="s">
         <v>480</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>462</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>482</v>
       </c>
       <c r="J21" s="39"/>
       <c r="K21" s="37" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L21" s="37" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="M21" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="35"/>
       <c r="B22" s="37"/>
       <c r="C22" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>484</v>
+      </c>
+      <c r="E22" s="37" t="s">
         <v>485</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="F22" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>479</v>
+      </c>
+      <c r="I22" s="37" t="s">
         <v>486</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>487</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>462</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>488</v>
       </c>
       <c r="J22" s="39"/>
       <c r="K22" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L22" s="37" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M22" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="35"/>
       <c r="B23" s="37"/>
       <c r="C23" s="37" t="s">
+        <v>488</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>489</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>490</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="F23" s="37" t="s">
         <v>491</v>
       </c>
-      <c r="E23" s="37" t="s">
+      <c r="G23" s="38" t="s">
         <v>492</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="H23" s="37" t="s">
         <v>493</v>
       </c>
-      <c r="G23" s="38" t="s">
+      <c r="I23" s="43" t="s">
         <v>494</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>495</v>
-      </c>
-      <c r="I23" s="43" t="s">
-        <v>496</v>
       </c>
       <c r="J23" s="39"/>
       <c r="K23" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L23" s="37" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M23" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="35"/>
       <c r="B24" s="37"/>
       <c r="C24" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="E24" s="37" t="s">
         <v>498</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="F24" s="37" t="s">
         <v>499</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="G24" s="38" t="s">
         <v>500</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="H24" s="37" t="s">
         <v>501</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="I24" s="37" t="s">
         <v>502</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>504</v>
       </c>
       <c r="J24" s="39"/>
       <c r="K24" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L24" s="37" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M24" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -11818,131 +11642,131 @@
       <c r="B25" s="37"/>
       <c r="C25" s="37"/>
       <c r="D25" s="37" t="s">
+        <v>504</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>505</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G25" s="38" t="s">
         <v>506</v>
       </c>
-      <c r="E25" s="37" t="s">
+      <c r="H25" s="37" t="s">
         <v>507</v>
       </c>
-      <c r="F25" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G25" s="38" t="s">
+      <c r="I25" s="37" t="s">
         <v>508</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>509</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>510</v>
       </c>
       <c r="J25" s="39"/>
       <c r="K25" s="37"/>
       <c r="L25" s="37"/>
       <c r="M25" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="35"/>
       <c r="B26" s="37"/>
       <c r="C26" s="37" t="s">
+        <v>509</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>510</v>
+      </c>
+      <c r="E26" s="37" t="s">
         <v>511</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="F26" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G26" s="38" t="s">
         <v>512</v>
       </c>
-      <c r="E26" s="37" t="s">
+      <c r="H26" s="37" t="s">
         <v>513</v>
       </c>
-      <c r="F26" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G26" s="38" t="s">
+      <c r="I26" s="37" t="s">
         <v>514</v>
       </c>
-      <c r="H26" s="37" t="s">
+      <c r="J26" s="39" t="s">
         <v>515</v>
       </c>
-      <c r="I26" s="37" t="s">
+      <c r="K26" s="37" t="s">
         <v>516</v>
       </c>
-      <c r="J26" s="39" t="s">
+      <c r="L26" s="37" t="s">
         <v>517</v>
       </c>
-      <c r="K26" s="37" t="s">
-        <v>518</v>
-      </c>
-      <c r="L26" s="37" t="s">
-        <v>519</v>
-      </c>
       <c r="M26" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="35"/>
       <c r="B27" s="37"/>
       <c r="C27" s="37" t="s">
+        <v>518</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>519</v>
+      </c>
+      <c r="E27" s="37" t="s">
         <v>520</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="F27" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G27" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="E27" s="37" t="s">
+      <c r="H27" s="37" t="s">
         <v>522</v>
       </c>
-      <c r="F27" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G27" s="38" t="s">
+      <c r="I27" s="37" t="s">
         <v>523</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>524</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>525</v>
       </c>
       <c r="J27" s="39"/>
       <c r="K27" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L27" s="37" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="M27" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="35"/>
       <c r="B28" s="37"/>
       <c r="C28" s="37" t="s">
+        <v>525</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>526</v>
+      </c>
+      <c r="E28" s="37" t="s">
         <v>527</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>528</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>529</v>
-      </c>
       <c r="F28" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="37"/>
       <c r="I28" s="37" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J28" s="39"/>
       <c r="K28" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L28" s="37" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M28" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -11950,35 +11774,35 @@
         <v>3551</v>
       </c>
       <c r="B29" s="37" t="s">
+        <v>530</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>531</v>
+      </c>
+      <c r="D29" s="37" t="s">
         <v>532</v>
       </c>
-      <c r="C29" s="37" t="s">
+      <c r="E29" s="37" t="s">
         <v>533</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="F29" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G29" s="38" t="s">
         <v>534</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="H29" s="37" t="s">
         <v>535</v>
       </c>
-      <c r="F29" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G29" s="38" t="s">
+      <c r="I29" s="37" t="s">
         <v>536</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>537</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>538</v>
       </c>
       <c r="J29" s="39"/>
       <c r="K29" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L29" s="37" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="M29" s="35"/>
     </row>
@@ -11986,70 +11810,70 @@
       <c r="A30" s="35"/>
       <c r="B30" s="37"/>
       <c r="C30" s="37" t="s">
+        <v>538</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>539</v>
+      </c>
+      <c r="E30" s="37" t="s">
         <v>540</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="F30" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G30" s="38" t="s">
         <v>541</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="H30" s="37" t="s">
         <v>542</v>
       </c>
-      <c r="F30" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G30" s="38" t="s">
+      <c r="I30" s="37" t="s">
         <v>543</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>545</v>
       </c>
       <c r="J30" s="39"/>
       <c r="K30" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L30" s="37" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="M30" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="35"/>
       <c r="B31" s="37"/>
       <c r="C31" s="37" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D31" s="37" t="s">
+        <v>545</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>546</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G31" s="38" t="s">
         <v>547</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="H31" s="37" t="s">
+        <v>542</v>
+      </c>
+      <c r="I31" s="37" t="s">
         <v>548</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>549</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>544</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>550</v>
       </c>
       <c r="J31" s="39"/>
       <c r="K31" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="M31" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -12057,35 +11881,35 @@
         <v>4827</v>
       </c>
       <c r="B32" s="37" t="s">
+        <v>550</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>551</v>
+      </c>
+      <c r="D32" s="37" t="s">
         <v>552</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="E32" s="37" t="s">
         <v>553</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="F32" s="37" t="s">
         <v>554</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="G32" s="38" t="s">
         <v>555</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="H32" s="37" t="s">
         <v>556</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="I32" s="37" t="s">
         <v>557</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>558</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>559</v>
       </c>
       <c r="J32" s="39"/>
       <c r="K32" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L32" s="37" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="M32" s="35"/>
     </row>
@@ -12094,28 +11918,28 @@
       <c r="B33" s="37"/>
       <c r="C33" s="37"/>
       <c r="D33" s="37" t="s">
+        <v>559</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>560</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G33" s="38" t="s">
         <v>561</v>
       </c>
-      <c r="E33" s="37" t="s">
+      <c r="H33" s="37" t="s">
+        <v>507</v>
+      </c>
+      <c r="I33" s="37" t="s">
         <v>562</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G33" s="38" t="s">
-        <v>563</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>509</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>564</v>
       </c>
       <c r="J33" s="39"/>
       <c r="K33" s="37"/>
       <c r="L33" s="37"/>
       <c r="M33" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -12123,61 +11947,61 @@
       <c r="B34" s="37"/>
       <c r="C34" s="37"/>
       <c r="D34" s="37" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E34" s="37" t="s">
+        <v>563</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>564</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>507</v>
+      </c>
+      <c r="I34" s="37" t="s">
         <v>565</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>566</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>509</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>567</v>
       </c>
       <c r="J34" s="39"/>
       <c r="K34" s="37"/>
       <c r="L34" s="37"/>
       <c r="M34" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="35"/>
       <c r="B35" s="37"/>
       <c r="C35" s="37" t="s">
+        <v>566</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>567</v>
+      </c>
+      <c r="E35" s="37" t="s">
         <v>568</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>569</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>570</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="38" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J35" s="39"/>
       <c r="K35" s="37" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L35" s="37" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="M35" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -12185,35 +12009,35 @@
         <v>2928</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D36" s="37" t="s">
+        <v>573</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>574</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G36" s="38" t="s">
         <v>575</v>
       </c>
-      <c r="E36" s="37" t="s">
+      <c r="H36" s="37" t="s">
         <v>576</v>
       </c>
-      <c r="F36" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G36" s="38" t="s">
+      <c r="I36" s="37" t="s">
         <v>577</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>578</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>579</v>
       </c>
       <c r="J36" s="39"/>
       <c r="K36" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L36" s="37" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M36" s="35"/>
     </row>
@@ -12221,62 +12045,62 @@
       <c r="A37" s="35"/>
       <c r="B37" s="37"/>
       <c r="C37" s="37" t="s">
+        <v>579</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>580</v>
+      </c>
+      <c r="E37" s="37" t="s">
         <v>581</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>582</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>583</v>
       </c>
       <c r="F37" s="37"/>
       <c r="G37" s="38" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H37" s="37"/>
       <c r="I37" s="37" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J37" s="39"/>
       <c r="K37" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L37" s="37" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="35"/>
       <c r="B38" s="37"/>
       <c r="C38" s="37" t="s">
+        <v>585</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>586</v>
+      </c>
+      <c r="E38" s="37" t="s">
         <v>587</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="F38" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G38" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="H38" s="37" t="s">
         <v>589</v>
       </c>
-      <c r="F38" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G38" s="38" t="s">
+      <c r="I38" s="37" t="s">
         <v>590</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>591</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>592</v>
       </c>
       <c r="J38" s="39"/>
       <c r="K38" s="37"/>
       <c r="L38" s="37"/>
       <c r="M38" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -12284,33 +12108,33 @@
         <v>6677</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C39" s="37" t="s">
+        <v>591</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>592</v>
+      </c>
+      <c r="E39" s="37" t="s">
         <v>593</v>
       </c>
-      <c r="D39" s="37" t="s">
-        <v>594</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>595</v>
-      </c>
       <c r="F39" s="37" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G39" s="38"/>
       <c r="H39" s="37" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J39" s="39" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K39" s="37"/>
       <c r="L39" s="37" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M39" s="35"/>
     </row>
@@ -12319,32 +12143,32 @@
       <c r="B40" s="37"/>
       <c r="C40" s="37"/>
       <c r="D40" s="37" t="s">
+        <v>597</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>598</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>564</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>507</v>
+      </c>
+      <c r="I40" s="37" t="s">
         <v>599</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>600</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G40" s="38" t="s">
-        <v>566</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>509</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>601</v>
       </c>
       <c r="J40" s="39"/>
       <c r="K40" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L40" s="37" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M40" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -12352,35 +12176,35 @@
         <v>3551</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C41" s="37" t="s">
+        <v>601</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>602</v>
+      </c>
+      <c r="E41" s="37" t="s">
         <v>603</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="F41" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G41" s="38" t="s">
         <v>604</v>
       </c>
-      <c r="E41" s="37" t="s">
+      <c r="H41" s="37" t="s">
         <v>605</v>
       </c>
-      <c r="F41" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G41" s="38" t="s">
+      <c r="I41" s="37" t="s">
         <v>606</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>607</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>608</v>
       </c>
       <c r="J41" s="39"/>
       <c r="K41" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L41" s="37" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="M41" s="35"/>
     </row>
@@ -12388,35 +12212,35 @@
       <c r="A42" s="35"/>
       <c r="B42" s="37"/>
       <c r="C42" s="37" t="s">
+        <v>608</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>609</v>
+      </c>
+      <c r="E42" s="37" t="s">
         <v>610</v>
       </c>
-      <c r="D42" s="37" t="s">
+      <c r="F42" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>609</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="I42" s="37" t="s">
         <v>611</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>612</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G42" s="38" t="s">
-        <v>611</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>515</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>613</v>
       </c>
       <c r="J42" s="39"/>
       <c r="K42" s="37" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L42" s="37" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="M42" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -12425,25 +12249,25 @@
       <c r="C43" s="37"/>
       <c r="D43" s="37"/>
       <c r="E43" s="37" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J43" s="39"/>
       <c r="K43" s="37"/>
       <c r="L43" s="37"/>
       <c r="M43" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -12452,25 +12276,25 @@
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
       <c r="E44" s="37" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G44" s="38" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="J44" s="39"/>
       <c r="K44" s="37"/>
       <c r="L44" s="37"/>
       <c r="M44" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -12479,25 +12303,25 @@
       <c r="C45" s="37"/>
       <c r="D45" s="37"/>
       <c r="E45" s="37" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="J45" s="39"/>
       <c r="K45" s="37"/>
       <c r="L45" s="37"/>
       <c r="M45" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -12506,60 +12330,60 @@
       <c r="C46" s="37"/>
       <c r="D46" s="37"/>
       <c r="E46" s="37" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="J46" s="39"/>
       <c r="K46" s="37"/>
       <c r="L46" s="37"/>
       <c r="M46" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="35"/>
       <c r="B47" s="37"/>
       <c r="C47" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="D47" s="37" t="s">
+        <v>621</v>
+      </c>
+      <c r="E47" s="37" t="s">
         <v>622</v>
       </c>
-      <c r="D47" s="37" t="s">
+      <c r="F47" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G47" s="38" t="s">
         <v>623</v>
       </c>
-      <c r="E47" s="37" t="s">
+      <c r="H47" s="37" t="s">
         <v>624</v>
       </c>
-      <c r="F47" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G47" s="38" t="s">
+      <c r="I47" s="37" t="s">
         <v>625</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>626</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>627</v>
       </c>
       <c r="J47" s="39"/>
       <c r="K47" s="37" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L47" s="37" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="M47" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -12567,33 +12391,33 @@
         <v>2719</v>
       </c>
       <c r="B48" s="37" t="s">
+        <v>627</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>628</v>
+      </c>
+      <c r="D48" s="37" t="s">
         <v>629</v>
       </c>
-      <c r="C48" s="37" t="s">
+      <c r="E48" s="37" t="s">
         <v>630</v>
       </c>
-      <c r="D48" s="37" t="s">
-        <v>631</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>632</v>
-      </c>
       <c r="F48" s="37" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G48" s="38"/>
       <c r="H48" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="I48" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="J48" s="39"/>
       <c r="K48" s="37" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L48" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M48" s="35"/>
     </row>
@@ -12601,66 +12425,66 @@
       <c r="A49" s="35"/>
       <c r="B49" s="37"/>
       <c r="C49" s="37" t="s">
+        <v>634</v>
+      </c>
+      <c r="D49" s="37" t="s">
+        <v>635</v>
+      </c>
+      <c r="E49" s="37" t="s">
         <v>636</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="F49" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G49" s="38" t="s">
         <v>637</v>
       </c>
-      <c r="E49" s="37" t="s">
+      <c r="H49" s="37" t="s">
         <v>638</v>
       </c>
-      <c r="F49" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G49" s="38" t="s">
-        <v>639</v>
-      </c>
-      <c r="H49" s="37" t="s">
-        <v>640</v>
-      </c>
       <c r="I49" s="37" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J49" s="39"/>
       <c r="K49" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L49" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="M49" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="35"/>
       <c r="B50" s="37"/>
       <c r="C50" s="37" t="s">
+        <v>640</v>
+      </c>
+      <c r="D50" s="37" t="s">
+        <v>635</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>641</v>
+      </c>
+      <c r="F50" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G50" s="38" t="s">
+        <v>637</v>
+      </c>
+      <c r="H50" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I50" s="37" t="s">
         <v>642</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>637</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>643</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G50" s="38" t="s">
-        <v>639</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>640</v>
-      </c>
-      <c r="I50" s="37" t="s">
-        <v>644</v>
       </c>
       <c r="J50" s="39"/>
       <c r="K50" s="37"/>
       <c r="L50" s="37"/>
       <c r="M50" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -12668,32 +12492,32 @@
       <c r="B51" s="37"/>
       <c r="C51" s="37"/>
       <c r="D51" s="37" t="s">
+        <v>643</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>644</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G51" s="38" t="s">
         <v>645</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="H51" s="37" t="s">
+        <v>507</v>
+      </c>
+      <c r="I51" s="37" t="s">
         <v>646</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G51" s="38" t="s">
-        <v>647</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>509</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>648</v>
       </c>
       <c r="J51" s="39"/>
       <c r="K51" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L51" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M51" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -12701,32 +12525,32 @@
       <c r="B52" s="37"/>
       <c r="C52" s="37"/>
       <c r="D52" s="37" t="s">
+        <v>648</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>649</v>
+      </c>
+      <c r="F52" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G52" s="38" t="s">
         <v>650</v>
       </c>
-      <c r="E52" s="37" t="s">
+      <c r="H52" s="37" t="s">
         <v>651</v>
       </c>
-      <c r="F52" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G52" s="38" t="s">
+      <c r="I52" s="37" t="s">
         <v>652</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>653</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>654</v>
       </c>
       <c r="J52" s="39"/>
       <c r="K52" s="37" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L52" s="37" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="M52" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -12734,35 +12558,35 @@
         <v>713</v>
       </c>
       <c r="B53" s="37" t="s">
+        <v>654</v>
+      </c>
+      <c r="C53" s="37" t="s">
+        <v>655</v>
+      </c>
+      <c r="D53" s="37" t="s">
         <v>656</v>
       </c>
-      <c r="C53" s="37" t="s">
+      <c r="E53" s="37" t="s">
         <v>657</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="F53" s="37" t="s">
+        <v>554</v>
+      </c>
+      <c r="G53" s="38" t="s">
         <v>658</v>
       </c>
-      <c r="E53" s="37" t="s">
+      <c r="H53" s="37" t="s">
         <v>659</v>
       </c>
-      <c r="F53" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="G53" s="38" t="s">
+      <c r="I53" s="37" t="s">
         <v>660</v>
-      </c>
-      <c r="H53" s="37" t="s">
-        <v>661</v>
-      </c>
-      <c r="I53" s="37" t="s">
-        <v>662</v>
       </c>
       <c r="J53" s="39"/>
       <c r="K53" s="37" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L53" s="37" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="M53" s="35"/>
     </row>
@@ -12771,35 +12595,35 @@
         <v>10294</v>
       </c>
       <c r="B54" s="37" t="s">
+        <v>662</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>663</v>
+      </c>
+      <c r="D54" s="37" t="s">
         <v>664</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="E54" s="37" t="s">
         <v>665</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="F54" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G54" s="38" t="s">
         <v>666</v>
       </c>
-      <c r="E54" s="37" t="s">
+      <c r="H54" s="37" t="s">
         <v>667</v>
       </c>
-      <c r="F54" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G54" s="38" t="s">
+      <c r="I54" s="37" t="s">
         <v>668</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>669</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>670</v>
       </c>
       <c r="J54" s="39"/>
       <c r="K54" s="37" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="L54" s="37" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="M54" s="35"/>
     </row>
@@ -12808,35 +12632,35 @@
         <v>4827</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C55" s="37" t="s">
+        <v>671</v>
+      </c>
+      <c r="D55" s="37" t="s">
+        <v>672</v>
+      </c>
+      <c r="E55" s="37" t="s">
         <v>673</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="F55" s="37" t="s">
+        <v>554</v>
+      </c>
+      <c r="G55" s="38" t="s">
         <v>674</v>
       </c>
-      <c r="E55" s="37" t="s">
+      <c r="H55" s="37" t="s">
         <v>675</v>
       </c>
-      <c r="F55" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="G55" s="38" t="s">
+      <c r="I55" s="37" t="s">
         <v>676</v>
-      </c>
-      <c r="H55" s="37" t="s">
-        <v>677</v>
-      </c>
-      <c r="I55" s="37" t="s">
-        <v>678</v>
       </c>
       <c r="J55" s="39"/>
       <c r="K55" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L55" s="37" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="M55" s="35"/>
     </row>
@@ -12844,56 +12668,56 @@
       <c r="A56" s="35"/>
       <c r="B56" s="37"/>
       <c r="C56" s="37" t="s">
+        <v>678</v>
+      </c>
+      <c r="D56" s="37" t="s">
+        <v>679</v>
+      </c>
+      <c r="E56" s="37" t="s">
         <v>680</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="F56" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G56" s="38" t="s">
         <v>681</v>
       </c>
-      <c r="E56" s="37" t="s">
+      <c r="H56" s="37" t="s">
+        <v>651</v>
+      </c>
+      <c r="I56" s="37" t="s">
         <v>682</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G56" s="38" t="s">
-        <v>683</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>653</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>684</v>
       </c>
       <c r="J56" s="39"/>
       <c r="K56" s="37"/>
       <c r="L56" s="37"/>
       <c r="M56" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="35"/>
       <c r="B57" s="37"/>
       <c r="C57" s="37" t="s">
+        <v>683</v>
+      </c>
+      <c r="D57" s="37" t="s">
+        <v>684</v>
+      </c>
+      <c r="E57" s="37" t="s">
         <v>685</v>
-      </c>
-      <c r="D57" s="37" t="s">
-        <v>686</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>687</v>
       </c>
       <c r="F57" s="37"/>
       <c r="G57" s="38"/>
       <c r="H57" s="37"/>
       <c r="I57" s="37" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J57" s="39"/>
       <c r="K57" s="37"/>
       <c r="L57" s="37"/>
       <c r="M57" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -12901,67 +12725,67 @@
       <c r="B58" s="37"/>
       <c r="C58" s="37"/>
       <c r="D58" s="37" t="s">
+        <v>687</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>688</v>
+      </c>
+      <c r="F58" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G58" s="38" t="s">
         <v>689</v>
       </c>
-      <c r="E58" s="37" t="s">
+      <c r="H58" s="37" t="s">
         <v>690</v>
       </c>
-      <c r="F58" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G58" s="38" t="s">
+      <c r="I58" s="37" t="s">
         <v>691</v>
-      </c>
-      <c r="H58" s="37" t="s">
-        <v>692</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>693</v>
       </c>
       <c r="J58" s="39"/>
       <c r="K58" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L58" s="37" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="M58" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="35"/>
       <c r="B59" s="37"/>
       <c r="C59" s="37" t="s">
+        <v>693</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>694</v>
+      </c>
+      <c r="E59" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="D59" s="37" t="s">
+      <c r="F59" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G59" s="38" t="s">
         <v>696</v>
       </c>
-      <c r="E59" s="37" t="s">
+      <c r="H59" s="37" t="s">
         <v>697</v>
       </c>
-      <c r="F59" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G59" s="38" t="s">
+      <c r="I59" s="37" t="s">
         <v>698</v>
-      </c>
-      <c r="H59" s="37" t="s">
-        <v>699</v>
-      </c>
-      <c r="I59" s="37" t="s">
-        <v>700</v>
       </c>
       <c r="J59" s="39"/>
       <c r="K59" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L59" s="37" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="M59" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -12969,59 +12793,59 @@
       <c r="B60" s="37"/>
       <c r="C60" s="37"/>
       <c r="D60" s="37" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G60" s="38"/>
       <c r="H60" s="37"/>
       <c r="I60" s="37" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="J60" s="39"/>
       <c r="K60" s="37"/>
       <c r="L60" s="37"/>
       <c r="M60" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="35"/>
       <c r="B61" s="37"/>
       <c r="C61" s="37" t="s">
+        <v>702</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>703</v>
+      </c>
+      <c r="E61" s="37" t="s">
         <v>704</v>
       </c>
-      <c r="D61" s="37" t="s">
+      <c r="F61" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G61" s="38" t="s">
         <v>705</v>
       </c>
-      <c r="E61" s="37" t="s">
+      <c r="H61" s="37" t="s">
         <v>706</v>
       </c>
-      <c r="F61" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G61" s="38" t="s">
+      <c r="I61" s="37" t="s">
         <v>707</v>
-      </c>
-      <c r="H61" s="37" t="s">
-        <v>708</v>
-      </c>
-      <c r="I61" s="37" t="s">
-        <v>709</v>
       </c>
       <c r="J61" s="39"/>
       <c r="K61" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L61" s="37" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="M61" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -13029,33 +12853,33 @@
         <v>3546</v>
       </c>
       <c r="B62" s="37" t="s">
+        <v>709</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>710</v>
+      </c>
+      <c r="D62" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="E62" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="D62" s="37" t="s">
+      <c r="F62" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G62" s="38" t="s">
         <v>713</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G62" s="38" t="s">
-        <v>715</v>
       </c>
       <c r="H62" s="37"/>
       <c r="I62" s="37" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="J62" s="39"/>
       <c r="K62" s="37" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L62" s="37" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="M62" s="35"/>
     </row>
@@ -13063,31 +12887,31 @@
       <c r="A63" s="35"/>
       <c r="B63" s="37"/>
       <c r="C63" s="37" t="s">
+        <v>716</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>717</v>
+      </c>
+      <c r="E63" s="37" t="s">
         <v>718</v>
       </c>
-      <c r="D63" s="37" t="s">
-        <v>719</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>720</v>
-      </c>
       <c r="F63" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="37"/>
       <c r="I63" s="37" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="J63" s="39"/>
       <c r="K63" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L63" s="37" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M63" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -13095,35 +12919,35 @@
         <v>61</v>
       </c>
       <c r="B64" s="37" t="s">
+        <v>721</v>
+      </c>
+      <c r="C64" s="37" t="s">
+        <v>722</v>
+      </c>
+      <c r="D64" s="37" t="s">
         <v>723</v>
       </c>
-      <c r="C64" s="37" t="s">
+      <c r="E64" s="37" t="s">
         <v>724</v>
       </c>
-      <c r="D64" s="37" t="s">
+      <c r="F64" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G64" s="38" t="s">
         <v>725</v>
       </c>
-      <c r="E64" s="37" t="s">
+      <c r="H64" s="37" t="s">
+        <v>493</v>
+      </c>
+      <c r="I64" s="37" t="s">
         <v>726</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G64" s="38" t="s">
-        <v>727</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>495</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>728</v>
       </c>
       <c r="J64" s="39"/>
       <c r="K64" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L64" s="37" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="M64" s="35"/>
     </row>
@@ -13131,70 +12955,70 @@
       <c r="A65" s="35"/>
       <c r="B65" s="37"/>
       <c r="C65" s="37" t="s">
+        <v>728</v>
+      </c>
+      <c r="D65" s="37" t="s">
+        <v>729</v>
+      </c>
+      <c r="E65" s="37" t="s">
         <v>730</v>
       </c>
-      <c r="D65" s="37" t="s">
+      <c r="F65" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G65" s="38" t="s">
         <v>731</v>
       </c>
-      <c r="E65" s="37" t="s">
+      <c r="H65" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="I65" s="37" t="s">
         <v>732</v>
-      </c>
-      <c r="F65" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G65" s="38" t="s">
-        <v>733</v>
-      </c>
-      <c r="H65" s="37" t="s">
-        <v>515</v>
-      </c>
-      <c r="I65" s="37" t="s">
-        <v>734</v>
       </c>
       <c r="J65" s="39"/>
       <c r="K65" s="37" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L65" s="37" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="M65" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="35"/>
       <c r="B66" s="37"/>
       <c r="C66" s="37" t="s">
+        <v>734</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>735</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>736</v>
       </c>
-      <c r="D66" s="37" t="s">
+      <c r="F66" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G66" s="38" t="s">
         <v>737</v>
       </c>
-      <c r="E66" s="37" t="s">
+      <c r="H66" s="37" t="s">
+        <v>589</v>
+      </c>
+      <c r="I66" s="37" t="s">
         <v>738</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G66" s="38" t="s">
-        <v>739</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>591</v>
-      </c>
-      <c r="I66" s="37" t="s">
-        <v>740</v>
       </c>
       <c r="J66" s="39"/>
       <c r="K66" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L66" s="37" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="M66" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -13202,35 +13026,35 @@
         <v>186</v>
       </c>
       <c r="B67" s="37" t="s">
+        <v>740</v>
+      </c>
+      <c r="C67" s="37" t="s">
+        <v>741</v>
+      </c>
+      <c r="D67" s="37" t="s">
         <v>742</v>
       </c>
-      <c r="C67" s="37" t="s">
+      <c r="E67" s="37" t="s">
         <v>743</v>
       </c>
-      <c r="D67" s="37" t="s">
+      <c r="F67" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G67" s="38" t="s">
         <v>744</v>
       </c>
-      <c r="E67" s="37" t="s">
+      <c r="H67" s="37" t="s">
+        <v>493</v>
+      </c>
+      <c r="I67" s="37" t="s">
         <v>745</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G67" s="38" t="s">
-        <v>746</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>495</v>
-      </c>
-      <c r="I67" s="37" t="s">
-        <v>747</v>
       </c>
       <c r="J67" s="39"/>
       <c r="K67" s="37" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L67" s="37" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="M67" s="35"/>
     </row>
@@ -13239,90 +13063,90 @@
       <c r="B68" s="37"/>
       <c r="C68" s="37"/>
       <c r="D68" s="37" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="F68" s="37"/>
       <c r="G68" s="38" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="H68" s="37"/>
       <c r="I68" s="37" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J68" s="39"/>
       <c r="K68" s="37"/>
       <c r="L68" s="37"/>
       <c r="M68" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="35"/>
       <c r="B69" s="37"/>
       <c r="C69" s="37" t="s">
+        <v>751</v>
+      </c>
+      <c r="D69" s="37" t="s">
+        <v>752</v>
+      </c>
+      <c r="E69" s="37" t="s">
         <v>753</v>
       </c>
-      <c r="D69" s="37" t="s">
+      <c r="F69" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G69" s="38" t="s">
         <v>754</v>
       </c>
-      <c r="E69" s="37" t="s">
+      <c r="H69" s="37" t="s">
         <v>755</v>
       </c>
-      <c r="F69" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G69" s="38" t="s">
+      <c r="I69" s="37" t="s">
         <v>756</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>757</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>758</v>
       </c>
       <c r="J69" s="39"/>
       <c r="K69" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L69" s="37" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="M69" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="35"/>
       <c r="B70" s="37"/>
       <c r="C70" s="37" t="s">
+        <v>758</v>
+      </c>
+      <c r="D70" s="37" t="s">
+        <v>759</v>
+      </c>
+      <c r="E70" s="37" t="s">
         <v>760</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>761</v>
-      </c>
-      <c r="E70" s="37" t="s">
-        <v>762</v>
       </c>
       <c r="F70" s="37"/>
       <c r="G70" s="38"/>
       <c r="H70" s="37" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J70" s="39"/>
       <c r="K70" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L70" s="37" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="M70" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -13330,33 +13154,33 @@
         <v>2701</v>
       </c>
       <c r="B71" s="37" t="s">
+        <v>764</v>
+      </c>
+      <c r="C71" s="37" t="s">
+        <v>765</v>
+      </c>
+      <c r="D71" s="37" t="s">
+        <v>629</v>
+      </c>
+      <c r="E71" s="37" t="s">
         <v>766</v>
-      </c>
-      <c r="C71" s="37" t="s">
-        <v>767</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>631</v>
-      </c>
-      <c r="E71" s="37" t="s">
-        <v>768</v>
       </c>
       <c r="F71" s="37"/>
       <c r="G71" s="38" t="s">
+        <v>767</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>768</v>
+      </c>
+      <c r="I71" s="37" t="s">
         <v>769</v>
-      </c>
-      <c r="H71" s="37" t="s">
-        <v>770</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>771</v>
       </c>
       <c r="J71" s="39"/>
       <c r="K71" s="37" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L71" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M71" s="35"/>
     </row>
@@ -13368,32 +13192,32 @@
         <v>266</v>
       </c>
       <c r="C72" s="37" t="s">
+        <v>770</v>
+      </c>
+      <c r="D72" s="37" t="s">
+        <v>771</v>
+      </c>
+      <c r="E72" s="37" t="s">
         <v>772</v>
       </c>
-      <c r="D72" s="37" t="s">
+      <c r="F72" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G72" s="38" t="s">
         <v>773</v>
       </c>
-      <c r="E72" s="37" t="s">
+      <c r="H72" s="37" t="s">
         <v>774</v>
       </c>
-      <c r="F72" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G72" s="38" t="s">
+      <c r="I72" s="37" t="s">
         <v>775</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>776</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>777</v>
       </c>
       <c r="J72" s="39"/>
       <c r="K72" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L72" s="37" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="M72" s="35"/>
     </row>
@@ -13401,66 +13225,66 @@
       <c r="A73" s="35"/>
       <c r="B73" s="37"/>
       <c r="C73" s="37" t="s">
+        <v>777</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>778</v>
+      </c>
+      <c r="E73" s="37" t="s">
         <v>779</v>
       </c>
-      <c r="D73" s="37" t="s">
+      <c r="F73" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G73" s="38" t="s">
         <v>780</v>
       </c>
-      <c r="E73" s="37" t="s">
+      <c r="H73" s="37" t="s">
         <v>781</v>
       </c>
-      <c r="F73" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G73" s="38" t="s">
+      <c r="I73" s="37" t="s">
         <v>782</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>783</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>784</v>
       </c>
       <c r="J73" s="39"/>
       <c r="K73" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L73" s="37" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="M73" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="35"/>
       <c r="B74" s="37"/>
       <c r="C74" s="37" t="s">
+        <v>784</v>
+      </c>
+      <c r="D74" s="37" t="s">
+        <v>785</v>
+      </c>
+      <c r="E74" s="37" t="s">
         <v>786</v>
-      </c>
-      <c r="D74" s="37" t="s">
-        <v>787</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>788</v>
       </c>
       <c r="F74" s="37"/>
       <c r="G74" s="38" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="J74" s="39"/>
       <c r="K74" s="37" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L74" s="37"/>
       <c r="M74" s="35" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -13468,38 +13292,38 @@
         <v>11117</v>
       </c>
       <c r="B75" s="37" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C75" s="37" t="s">
+        <v>789</v>
+      </c>
+      <c r="D75" s="37" t="s">
+        <v>790</v>
+      </c>
+      <c r="E75" s="37" t="s">
         <v>791</v>
       </c>
-      <c r="D75" s="37" t="s">
+      <c r="F75" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="G75" s="38" t="s">
         <v>792</v>
       </c>
-      <c r="E75" s="37" t="s">
+      <c r="H75" s="37" t="s">
         <v>793</v>
       </c>
-      <c r="F75" s="37" t="s">
-        <v>501</v>
-      </c>
-      <c r="G75" s="38" t="s">
+      <c r="I75" s="37" t="s">
         <v>794</v>
-      </c>
-      <c r="H75" s="37" t="s">
-        <v>795</v>
-      </c>
-      <c r="I75" s="37" t="s">
-        <v>796</v>
       </c>
       <c r="J75" s="39"/>
       <c r="K75" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L75" s="37" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="M75" s="35" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -13507,35 +13331,35 @@
         <v>4827</v>
       </c>
       <c r="B76" s="37" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C76" s="37" t="s">
+        <v>797</v>
+      </c>
+      <c r="D76" s="37" t="s">
+        <v>798</v>
+      </c>
+      <c r="E76" s="37" t="s">
         <v>799</v>
       </c>
-      <c r="D76" s="37" t="s">
+      <c r="F76" s="37" t="s">
+        <v>554</v>
+      </c>
+      <c r="G76" s="38" t="s">
         <v>800</v>
       </c>
-      <c r="E76" s="37" t="s">
-        <v>801</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="G76" s="38" t="s">
-        <v>802</v>
-      </c>
       <c r="H76" s="37" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J76" s="39"/>
       <c r="K76" s="37" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L76" s="37" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="M76" s="35"/>
     </row>
@@ -13543,32 +13367,32 @@
       <c r="A77" s="28"/>
       <c r="B77" s="28"/>
       <c r="C77" s="28" t="s">
+        <v>802</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>803</v>
+      </c>
+      <c r="E77" s="28" t="s">
         <v>804</v>
       </c>
-      <c r="D77" s="28" t="s">
+      <c r="F77" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="G77" s="44" t="s">
         <v>805</v>
       </c>
-      <c r="E77" s="28" t="s">
+      <c r="H77" s="28" t="s">
         <v>806</v>
       </c>
-      <c r="F77" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="G77" s="44" t="s">
-        <v>807</v>
-      </c>
-      <c r="H77" s="28" t="s">
-        <v>808</v>
-      </c>
       <c r="I77" s="28" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J77" s="28"/>
       <c r="K77" s="28" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L77" s="28" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="M77" s="28"/>
     </row>
@@ -13577,35 +13401,35 @@
         <v>6677</v>
       </c>
       <c r="B78" s="37" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C78" s="28" t="s">
+        <v>808</v>
+      </c>
+      <c r="D78" s="28" t="s">
+        <v>809</v>
+      </c>
+      <c r="E78" s="28" t="s">
         <v>810</v>
       </c>
-      <c r="D78" s="28" t="s">
+      <c r="F78" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="G78" s="44" t="s">
         <v>811</v>
       </c>
-      <c r="E78" s="28" t="s">
+      <c r="H78" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="I78" s="28" t="s">
         <v>812</v>
-      </c>
-      <c r="F78" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="G78" s="44" t="s">
-        <v>813</v>
-      </c>
-      <c r="H78" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="I78" s="28" t="s">
-        <v>814</v>
       </c>
       <c r="J78" s="28"/>
       <c r="K78" s="28" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L78" s="28" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="M78" s="28"/>
     </row>
@@ -13614,34 +13438,34 @@
         <v>12731</v>
       </c>
       <c r="B79" s="28" t="s">
+        <v>814</v>
+      </c>
+      <c r="C79" s="28" t="s">
+        <v>815</v>
+      </c>
+      <c r="D79" s="28" t="s">
         <v>816</v>
       </c>
-      <c r="C79" s="28" t="s">
+      <c r="E79" s="28" t="s">
         <v>817</v>
       </c>
-      <c r="D79" s="28" t="s">
+      <c r="F79" s="28" t="s">
+        <v>499</v>
+      </c>
+      <c r="G79" s="44" t="s">
         <v>818</v>
       </c>
-      <c r="E79" s="28" t="s">
+      <c r="H79" s="28" t="s">
         <v>819</v>
       </c>
-      <c r="F79" s="28" t="s">
-        <v>501</v>
-      </c>
-      <c r="G79" s="44" t="s">
+      <c r="I79" s="28" t="s">
         <v>820</v>
       </c>
-      <c r="H79" s="28" t="s">
+      <c r="J79" s="28" t="s">
         <v>821</v>
       </c>
-      <c r="I79" s="28" t="s">
-        <v>822</v>
-      </c>
-      <c r="J79" s="28" t="s">
-        <v>823</v>
-      </c>
       <c r="K79" s="28" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L79" s="28"/>
       <c r="M79" s="28"/>
@@ -25666,7 +25490,7 @@
         <v>8</v>
       </c>
       <c r="H1" s="45" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I1" s="45" t="s">
         <v>10</v>
@@ -25678,10 +25502,10 @@
         <v>12</v>
       </c>
       <c r="L1" s="46" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="M1" s="46" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -25690,69 +25514,69 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>827</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>829</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>830</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>832</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>833</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>834</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>835</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>836</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>839</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>840</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>841</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>842</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>832</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>834</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>843</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>844</v>
       </c>
     </row>
   </sheetData>
